--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.2</v>
+        <v>27.5</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="3">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>27.8</v>
+        <v>28.1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="4">
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>68.3</t>
+          <t>73.4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>26.6</v>
+        <v>26.9</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="5">
@@ -532,19 +532,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>27.4</v>
+        <v>27.7</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>71.9</t>
+          <t>77.2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>27</v>
+        <v>27.3</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>75.5</t>
+          <t>81.1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>28</v>
+        <v>28.4</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,19 +463,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>27.5</v>
+        <v>29.8</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="3">
@@ -486,19 +486,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>28.1</v>
+        <v>30.6</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="4">
@@ -509,19 +509,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>73.4</t>
+          <t>89.6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>26.9</v>
+        <v>29.1</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="5">
@@ -532,19 +532,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>27.7</v>
+        <v>30.1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>77.2</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>27.3</v>
+        <v>29.6</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>81.1</t>
+          <t>99.1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>28.4</v>
+        <v>30.9</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,19 +463,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29.8</v>
+        <v>28.8</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="3">
@@ -486,19 +486,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>106.1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>30.6</v>
+        <v>29.7</v>
       </c>
       <c r="E3" t="n">
-        <v>1.7</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="4">
@@ -509,19 +509,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>89.6</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>29.1</v>
+        <v>28</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="5">
@@ -532,19 +532,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30.1</v>
+        <v>29.1</v>
       </c>
       <c r="E5" t="n">
-        <v>1.2</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>29.6</v>
+        <v>28.5</v>
       </c>
       <c r="E6" t="n">
-        <v>0.7</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>99.1</t>
+          <t>106.1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>30.9</v>
+        <v>30</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>28.8</v>
+        <v>29.1</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="3">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>29.7</v>
+        <v>30</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="4">
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>28</v>
+        <v>28.3</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="5">
@@ -541,10 +541,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29.1</v>
+        <v>29.4</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>28.5</v>
+        <v>28.8</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="7">
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>30</v>
+        <v>30.3</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,19 +463,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>103.8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29.1</v>
+        <v>30.7</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -486,19 +486,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>106.1</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>30</v>
+        <v>31.5</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="4">
@@ -509,19 +509,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>98.6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>28.3</v>
+        <v>29.8</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="5">
@@ -532,19 +532,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>103.8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29.4</v>
+        <v>31</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>103.8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.3</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>28.8</v>
+        <v>30.3</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>106.1</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>30.3</v>
+        <v>31.9</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>121.9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.7</v>
+        <v>32.9</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31.5</v>
+        <v>33.9</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="4">
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>98.6</t>
+          <t>115.8</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>29.8</v>
+        <v>31.9</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="5">
@@ -532,19 +532,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>121.9</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>32.6</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31</v>
+        <v>33.3</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="6">
@@ -555,7 +555,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>103.8</t>
+          <t>121.9</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>30.3</v>
+        <v>32.5</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>128.0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>32.6</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>31.9</v>
+        <v>34.3</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>121.9</t>
+          <t>127.6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32.9</v>
+        <v>32.2</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="3">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>33.9</v>
+        <v>33.2</v>
       </c>
       <c r="E3" t="n">
-        <v>1.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="4">
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>115.8</t>
+          <t>121.2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>31.9</v>
+        <v>31.2</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="5">
@@ -532,7 +532,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>121.9</t>
+          <t>127.6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -541,10 +541,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>33.3</v>
+        <v>32.6</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="6">
@@ -555,7 +555,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>121.9</t>
+          <t>127.6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>32.5</v>
+        <v>31.8</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="7">
@@ -578,7 +578,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>128.0</t>
+          <t>134.0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>34.3</v>
+        <v>33.7</v>
       </c>
       <c r="E7" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,19 +463,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>127.6</t>
+          <t>123.3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32.2</v>
+        <v>32.5</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="3">
@@ -486,19 +486,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>129.4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>33.2</v>
+        <v>33.5</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="4">
@@ -509,19 +509,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>121.2</t>
+          <t>117.1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.8</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>31.2</v>
+        <v>31.5</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.2</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="5">
@@ -532,19 +532,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>127.6</t>
+          <t>123.3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.6</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>32.6</v>
+        <v>32.9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>127.6</t>
+          <t>123.3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.3</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31.8</v>
+        <v>32.1</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>134.0</t>
+          <t>129.4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.6</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>33.7</v>
+        <v>33.9</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,19 +463,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>123.3</t>
+          <t>103.4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32.5</v>
+        <v>31.6</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="3">
@@ -486,19 +486,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>129.4</t>
+          <t>108.6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>33.5</v>
+        <v>32.4</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -509,19 +509,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>117.1</t>
+          <t>98.2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>31.8</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>31.5</v>
+        <v>30.7</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9</v>
+        <v>-1.7</v>
       </c>
     </row>
     <row r="5">
@@ -532,19 +532,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>123.3</t>
+          <t>103.4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>32.9</v>
+        <v>31.9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>123.3</t>
+          <t>103.4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>32.1</v>
+        <v>31.2</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>129.4</t>
+          <t>108.6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>33.9</v>
+        <v>32.8</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5</v>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,19 +463,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>103.4</t>
+          <t>113.9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31.6</v>
+        <v>32.5</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.8</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="3">
@@ -486,19 +486,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>108.6</t>
+          <t>119.6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32.4</v>
+        <v>33.5</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="4">
@@ -509,19 +509,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>98.2</t>
+          <t>108.2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>30.7</v>
+        <v>31.6</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.7</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="5">
@@ -532,19 +532,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>103.4</t>
+          <t>113.9</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31.9</v>
+        <v>32.9</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>103.4</t>
+          <t>113.9</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31.2</v>
+        <v>32.2</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>108.6</t>
+          <t>119.6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>32.8</v>
+        <v>33.9</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4</v>
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,19 +463,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>113.9</t>
+          <t>118.3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32.5</v>
+        <v>31.9</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="3">
@@ -486,19 +486,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>119.6</t>
+          <t>124.2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>33.5</v>
+        <v>32.9</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4">
@@ -509,19 +509,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>108.2</t>
+          <t>112.3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>31.6</v>
+        <v>30.9</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="5">
@@ -532,19 +532,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>113.9</t>
+          <t>118.3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>32.9</v>
+        <v>32.3</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="6">
@@ -555,7 +555,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>113.9</t>
+          <t>118.3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>32.2</v>
+        <v>31.5</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>119.6</t>
+          <t>124.2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>33.9</v>
+        <v>33.3</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,19 +463,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>118.3</t>
+          <t>106.1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31.9</v>
+        <v>32.5</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="3">
@@ -486,19 +486,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>124.2</t>
+          <t>111.4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32.9</v>
+        <v>33.4</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -509,19 +509,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>100.8</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>30.9</v>
+        <v>31.6</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.5</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="5">
@@ -532,19 +532,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>118.3</t>
+          <t>106.1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>32.3</v>
+        <v>32.8</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>118.3</t>
+          <t>106.1</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31.5</v>
+        <v>32.2</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>124.2</t>
+          <t>111.4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>33.3</v>
+        <v>33.7</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,19 +463,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>106.1</t>
+          <t>116.7</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32.5</v>
+        <v>32.4</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -486,12 +486,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>111.4</t>
+          <t>122.6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -509,19 +509,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>100.8</t>
+          <t>110.9</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>31.6</v>
+        <v>31.5</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="5">
@@ -532,12 +532,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>106.1</t>
+          <t>116.7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -555,19 +555,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>106.1</t>
+          <t>116.7</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>32.2</v>
+        <v>32.1</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>111.4</t>
+          <t>122.6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>33.7</v>
+        <v>33.8</v>
       </c>
       <c r="E7" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,19 +463,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>116.7</t>
+          <t>102.8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32.4</v>
+        <v>32</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="3">
@@ -486,19 +486,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>122.6</t>
+          <t>107.9</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>33.4</v>
+        <v>32.9</v>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4">
@@ -509,19 +509,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>110.9</t>
+          <t>97.6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>31.5</v>
+        <v>31.2</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="5">
@@ -532,19 +532,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>116.7</t>
+          <t>102.8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>32.8</v>
+        <v>32.4</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>116.7</t>
+          <t>102.8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>30.8</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>32.1</v>
+        <v>31.7</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>122.6</t>
+          <t>107.9</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>33.8</v>
+        <v>33.2</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>102.8</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32</v>
+        <v>32.8</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.4</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="3">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>107.9</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32.9</v>
+        <v>33.6</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="4">
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>97.6</t>
+          <t>93.4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>31.2</v>
+        <v>32</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.2</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="5">
@@ -532,19 +532,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>102.8</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>32.4</v>
+        <v>33.1</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>102.8</t>
+          <t>98.3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>30.7</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31.7</v>
+        <v>32.5</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.7</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>107.9</t>
+          <t>103.2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>33.2</v>
+        <v>33.9</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8</v>
+        <v>1.5</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,19 +463,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32.8</v>
+        <v>32.2</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="3">
@@ -486,19 +486,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>102.3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>33.6</v>
+        <v>33</v>
       </c>
       <c r="E3" t="n">
-        <v>1.2</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="4">
@@ -509,19 +509,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>93.4</t>
+          <t>92.6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>31.5</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>32</v>
+        <v>31.4</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
@@ -532,19 +532,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>33.1</v>
+        <v>32.5</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>98.3</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>30.7</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>32.5</v>
+        <v>31.9</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>103.2</t>
+          <t>102.3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>33.9</v>
+        <v>33.3</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,19 +463,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="3">
@@ -486,12 +486,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>102.3</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -509,19 +509,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>92.6</t>
+          <t>80.1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>31.5</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>31.4</v>
+        <v>31.6</v>
       </c>
       <c r="E4" t="n">
-        <v>-1</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="5">
@@ -532,12 +532,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>32.3</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -555,19 +555,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31.9</v>
+        <v>32</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="7">
@@ -578,12 +578,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>102.3</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>32.3</t>
         </is>
       </c>
       <c r="D7" t="n">

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32.3</v>
+        <v>31.9</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="3">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>33</v>
+        <v>32.5</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="4">
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>80.1</t>
+          <t>72.7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>31.6</v>
+        <v>31.3</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.8</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="5">
@@ -532,19 +532,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>32.5</v>
+        <v>32.1</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.0</t>
+          <t>30.9</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>32</v>
+        <v>31.6</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>80.3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>33.3</v>
+        <v>32.8</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,19 +463,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>31.9</v>
+        <v>30.5</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="3">
@@ -486,19 +486,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32.5</v>
+        <v>31.1</v>
       </c>
       <c r="E3" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="4">
@@ -509,19 +509,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>72.7</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>31.3</v>
+        <v>29.9</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.1</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="5">
@@ -532,19 +532,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>32.1</v>
+        <v>30.7</v>
       </c>
       <c r="E5" t="n">
-        <v>0.7</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>71.6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>30.9</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>31.6</v>
+        <v>30.3</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80.3</t>
+          <t>75.2</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>32.8</v>
+        <v>31.3</v>
       </c>
       <c r="E7" t="n">
-        <v>1.4</v>
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.5</v>
+        <v>30.1</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="3">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31.1</v>
+        <v>30.7</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="4">
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>29.9</v>
+        <v>29.5</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="5">
@@ -532,7 +532,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -541,10 +541,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30.7</v>
+        <v>30.3</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -555,7 +555,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>71.6</t>
+          <t>69.6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>30.3</v>
+        <v>29.9</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="7">
@@ -578,7 +578,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>75.2</t>
+          <t>73.0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>31.3</v>
+        <v>30.9</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,19 +463,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.1</v>
+        <v>29.5</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="3">
@@ -486,19 +486,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>30.7</v>
+        <v>30.1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="4">
@@ -509,19 +509,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>77.5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>32.1</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>29.5</v>
+        <v>28.8</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.3</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
@@ -532,19 +532,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30.3</v>
+        <v>29.7</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>69.6</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>29.9</v>
+        <v>29.2</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>73.0</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>30.9</v>
+        <v>30.5</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,19 +463,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29.5</v>
+        <v>29.8</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -486,19 +486,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>30.1</v>
+        <v>30.6</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="4">
@@ -509,19 +509,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>77.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>32.1</t>
+          <t>32.4</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>28.8</v>
+        <v>29.1</v>
       </c>
       <c r="E4" t="n">
-        <v>-1</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="5">
@@ -532,19 +532,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>29.7</v>
+        <v>30.1</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>31.7</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>29.2</v>
+        <v>29.6</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.6</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>33.0</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>30.5</v>
+        <v>30.8</v>
       </c>
       <c r="E7" t="n">
-        <v>0.7</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="3">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>96.4</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -498,7 +498,7 @@
         <v>30.6</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="4">
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -521,7 +521,7 @@
         <v>29.1</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7</v>
+        <v>-1.4</v>
       </c>
     </row>
     <row r="5">
@@ -532,7 +532,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -541,10 +541,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="6">
@@ -555,7 +555,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>91.8</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -567,7 +567,7 @@
         <v>29.6</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.2</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="7">
@@ -578,7 +578,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>96.4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,19 +463,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>32.3</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>29.9</v>
+        <v>30.7</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.6</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="3">
@@ -486,19 +486,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>96.4</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>32.3</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>30.6</v>
+        <v>31.4</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="4">
@@ -509,19 +509,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>32.4</t>
+          <t>32.3</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>29.1</v>
+        <v>30</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.4</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="5">
@@ -532,19 +532,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30.2</v>
+        <v>31</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>91.8</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.7</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>29.6</v>
+        <v>30.4</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.9</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>96.4</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>33.0</t>
+          <t>32.9</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>30.9</v>
+        <v>31.7</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4</v>
+        <v>1.2</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,19 +463,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.7</v>
+        <v>30.4</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="3">
@@ -486,19 +486,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31.4</v>
+        <v>31.2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="4">
@@ -509,19 +509,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>32.3</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>30</v>
+        <v>29.6</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="5">
@@ -532,7 +532,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -541,10 +541,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31</v>
+        <v>30.7</v>
       </c>
       <c r="E5" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="6">
@@ -555,7 +555,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>93.3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>30.4</v>
+        <v>30.1</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.1</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="7">
@@ -578,7 +578,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>97.9</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -587,10 +587,10 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>31.7</v>
+        <v>31.5</v>
       </c>
       <c r="E7" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,19 +463,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="3">
@@ -486,19 +486,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>100.1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31.2</v>
+        <v>31.1</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="4">
@@ -509,19 +509,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.0</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.9</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
@@ -532,19 +532,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30.7</v>
+        <v>30.6</v>
       </c>
       <c r="E5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>93.3</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.6</t>
+          <t>31.4</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.4</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>97.9</t>
+          <t>100.1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>32.7</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,19 +463,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.3</v>
+        <v>30.5</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -486,19 +486,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>100.1</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="4">
@@ -509,19 +509,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>83.8</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>32.0</t>
+          <t>31.9</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>29.5</v>
+        <v>29.8</v>
       </c>
       <c r="E4" t="n">
-        <v>-1</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="5">
@@ -532,19 +532,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30.6</v>
+        <v>30.8</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.4</t>
+          <t>31.2</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>30</v>
+        <v>30.2</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100.1</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.7</t>
+          <t>32.5</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,19 +463,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.5</v>
+        <v>30.3</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="3">
@@ -486,19 +486,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>100.8</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31.2</v>
+        <v>31</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="4">
@@ -509,19 +509,19 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>83.8</t>
+          <t>91.2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>31.9</t>
+          <t>31.6</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>29.8</v>
+        <v>29.5</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.7</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="5">
@@ -532,19 +532,19 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>30.8</v>
+        <v>30.6</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="6">
@@ -555,19 +555,19 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>31.2</t>
+          <t>31.0</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>30.2</v>
+        <v>30</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.3</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>100.8</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.5</t>
+          <t>32.2</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>31.5</v>
+        <v>31.4</v>
       </c>
       <c r="E7" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
   </sheetData>

--- a/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
+++ b/週五精準預測成果/SENSITIVITY_ANALYSIS.xlsx
@@ -463,7 +463,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -472,10 +472,10 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.3</v>
+        <v>30.2</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.2</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="3">
@@ -486,7 +486,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>100.8</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>31</v>
+        <v>31.2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="4">
@@ -509,7 +509,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>91.2</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -518,10 +518,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="E4" t="n">
-        <v>-1</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="5">
@@ -532,12 +532,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.3</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -555,7 +555,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>109.5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -564,10 +564,10 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5</v>
+        <v>-0.6</v>
       </c>
     </row>
     <row r="7">
@@ -578,19 +578,19 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>100.8</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>32.2</t>
+          <t>32.3</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>31.4</v>
+        <v>31.5</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
